--- a/business_forms/047_uniform_style_guide_submission--business_forms.xlsx
+++ b/business_forms/047_uniform_style_guide_submission--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'style_1',_'value':_'style_1'}</t>
+          <t>style_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Style 1', 'value': 'style 1'}</t>
+          <t>Style 1</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'style_2',_'value':_'style_2'}</t>
+          <t>style_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Style 2', 'value': 'style 2'}</t>
+          <t>Style 2</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'style_3',_'value':_'style_3'}</t>
+          <t>style_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Style 3', 'value': 'style 3'}</t>
+          <t>Style 3</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'color_1',_'value':_'color_1'}</t>
+          <t>color_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Color 1', 'value': 'color 1'}</t>
+          <t>Color 1</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'color_2',_'value':_'color_2'}</t>
+          <t>color_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Color 2', 'value': 'color 2'}</t>
+          <t>Color 2</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'color_3',_'value':_'color_3'}</t>
+          <t>color_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Color 3', 'value': 'color 3'}</t>
+          <t>Color 3</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
